--- a/diseases/d093/2015-2019.xlsx
+++ b/diseases/d093/2015-2019.xlsx
@@ -67755,17 +67755,15 @@
       <c r="O497" t="n">
         <v>1</v>
       </c>
+      <c r="P497" t="n">
+        <v>1</v>
+      </c>
       <c r="Q497" t="n">
         <v>0</v>
       </c>
       <c r="R497" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S497" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA497" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -67778,22 +67776,12 @@
       </c>
       <c r="AP497" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR497" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS497" t="inlineStr"/>
       <c r="AT497" t="n">
         <v>0</v>
-      </c>
-      <c r="AU497" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV497" t="inlineStr">
         <is>
@@ -67908,17 +67896,15 @@
       <c r="O498" t="n">
         <v>1</v>
       </c>
+      <c r="P498" t="n">
+        <v>1</v>
+      </c>
       <c r="Q498" t="n">
         <v>0</v>
       </c>
       <c r="R498" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S498" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA498" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -67931,22 +67917,12 @@
       </c>
       <c r="AP498" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR498" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS498" t="inlineStr"/>
       <c r="AT498" t="n">
         <v>0</v>
-      </c>
-      <c r="AU498" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV498" t="inlineStr">
         <is>
@@ -72933,17 +72909,15 @@
       <c r="O535" t="n">
         <v>1</v>
       </c>
+      <c r="P535" t="n">
+        <v>1</v>
+      </c>
       <c r="Q535" t="n">
         <v>0</v>
       </c>
       <c r="R535" t="n">
         <v>0.0002960418612546737</v>
       </c>
-      <c r="S535" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA535" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -72956,22 +72930,12 @@
       </c>
       <c r="AP535" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR535" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS535" t="inlineStr"/>
       <c r="AT535" t="n">
         <v>0</v>
-      </c>
-      <c r="AU535" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV535" t="inlineStr">
         <is>
